--- a/графики/отчеты для СН/дефицит/недогруз Мариуполь.xlsx
+++ b/графики/отчеты для СН/дефицит/недогруз Мариуполь.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\отчеты для СН\дефицит\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\отчеты для СН\дефицит\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1206FD8-F88E-4E22-9AA5-EE791BEB3ED6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA013C7D-6699-4F9B-96E2-9E0E74507840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Останкино" sheetId="1" r:id="rId1"/>
@@ -26,23 +26,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Останкино!$A$1:$B$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ПОКОМ!$A$1:$B$39</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="141">
   <si>
     <t xml:space="preserve"> 005  Колбаса Докторская ГОСТ, Вязанка вектор,ВЕС. ПОКОМ</t>
   </si>
@@ -422,7 +411,49 @@
     <t>списано 100кг (пересчет 28,10,26)</t>
   </si>
   <si>
-    <t>????</t>
+    <t>списано 90кг (пересчет 28,10,26)</t>
+  </si>
+  <si>
+    <t>списание по срокам 68кг (27,10,26)</t>
+  </si>
+  <si>
+    <t>списано 54кг (пересчет 28,10,26)</t>
+  </si>
+  <si>
+    <t>списано 86кг (пересчет 28,10,26)</t>
+  </si>
+  <si>
+    <t>списание по срокам 42кг (27,10,26)</t>
+  </si>
+  <si>
+    <t>списание по срокам 53кг (27,10,26)</t>
+  </si>
+  <si>
+    <t>списано 47кг (пересчет 28,10,26)</t>
+  </si>
+  <si>
+    <t>списано 52кг (пересчет 28,10,26)</t>
+  </si>
+  <si>
+    <t>списано 46кг (пересчет 28,10,26)</t>
+  </si>
+  <si>
+    <t>Остаток, кг</t>
+  </si>
+  <si>
+    <t>матрица</t>
+  </si>
+  <si>
+    <t>рост продаж в 1,8 раза</t>
+  </si>
+  <si>
+    <t>продукция оприходована на выведенное скю - "Круггетсы с сырным соусом ТМ Горячая штучка 0,25 кг зам  ПОКОМ" - 87кг</t>
+  </si>
+  <si>
+    <t>дубль</t>
+  </si>
+  <si>
+    <t>торгуем данным скю в Мариуполе 2-ю неделю</t>
   </si>
 </sst>
 </file>
@@ -433,7 +464,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Arial"/>
@@ -451,6 +482,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -500,7 +538,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -524,7 +562,31 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -543,7 +605,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -3354,8 +3416,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="TDSheet"/>
     </sheetNames>
@@ -13011,9 +13076,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -13051,9 +13116,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -13086,26 +13151,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -13138,26 +13186,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -13340,8 +13371,9 @@
   <cols>
     <col min="1" max="1" width="82.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="37" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="57.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -13351,7 +13383,7 @@
       <c r="B1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -13362,22 +13394,24 @@
       <c r="B2" s="6">
         <v>1</v>
       </c>
+      <c r="D2"/>
     </row>
     <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="12">
         <v>3.2</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" s="11" t="str">
         <f>VLOOKUP(A3,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="13">
         <f>VLOOKUP(A3,[2]TDSheet!$A:$T,14,0)</f>
         <v>15.2</v>
       </c>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -13386,38 +13420,43 @@
       <c r="B4" s="4">
         <v>1.226</v>
       </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="12">
         <v>2.6</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5" s="11" t="str">
         <f>VLOOKUP(A5,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="13">
         <f>VLOOKUP(A5,[2]TDSheet!$A:$T,14,0)</f>
         <v>379.34300000000002</v>
       </c>
+      <c r="E5" s="11"/>
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="14">
         <v>5.8929999999999998</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C6" s="11" t="str">
         <f>VLOOKUP(A6,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="13">
         <f>VLOOKUP(A6,[2]TDSheet!$A:$T,14,0)</f>
         <v>89.277000000000001</v>
       </c>
+      <c r="E6" s="11"/>
     </row>
     <row r="7" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -13426,23 +13465,24 @@
       <c r="B7" s="4">
         <v>0.40799999999999997</v>
       </c>
+      <c r="D7"/>
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="11">
         <v>5.75</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C8" s="11" t="str">
         <f>VLOOKUP(A8,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="13">
         <f>VLOOKUP(A8,[2]TDSheet!$A:$T,14,0)</f>
         <v>0</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="11" t="s">
         <v>120</v>
       </c>
     </row>
@@ -13450,26 +13490,29 @@
       <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <v>0.43</v>
       </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="11">
         <v>11.5</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C10" s="11" t="str">
         <f>VLOOKUP(A10,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="13">
         <f>VLOOKUP(A10,[2]TDSheet!$A:$T,14,0)</f>
         <v>0</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="11" t="s">
         <v>121</v>
       </c>
     </row>
@@ -13477,26 +13520,29 @@
       <c r="A11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="3">
         <v>1.6</v>
       </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="11">
         <v>4.2</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C12" s="11" t="str">
         <f>VLOOKUP(A12,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="13">
         <f>VLOOKUP(A12,[2]TDSheet!$A:$T,14,0)</f>
         <v>0</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="11" t="s">
         <v>122</v>
       </c>
     </row>
@@ -13504,614 +13550,684 @@
       <c r="A13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="3">
         <v>1.5</v>
       </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="3">
         <v>1.2</v>
       </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="11">
         <v>5.0599999999999996</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C15" s="11" t="str">
         <f>VLOOKUP(A15,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="13">
         <f>VLOOKUP(A15,[2]TDSheet!$A:$T,14,0)</f>
         <v>0</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="11" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="11">
         <v>2.5</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C16" s="11" t="str">
         <f>VLOOKUP(A16,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="13">
         <f>VLOOKUP(A16,[2]TDSheet!$A:$T,14,0)</f>
         <v>60.707999999999998</v>
       </c>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="11">
         <v>10</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C17" s="11" t="str">
         <f>VLOOKUP(A17,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="13">
         <f>VLOOKUP(A17,[2]TDSheet!$A:$T,14,0)</f>
         <v>18.399999999999999</v>
       </c>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="11">
         <v>23.2</v>
       </c>
-      <c r="C18" t="str">
+      <c r="C18" s="11" t="str">
         <f>VLOOKUP(A18,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="13">
         <v>0</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="11" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="11">
         <v>14.4</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C19" s="11" t="str">
         <f>VLOOKUP(A19,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="13">
         <f>VLOOKUP(A19,[2]TDSheet!$A:$T,14,0)</f>
         <v>6.4</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="11" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="11">
         <v>16.2</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="15" t="s">
         <v>118</v>
       </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="3">
         <v>2</v>
       </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="11">
         <v>22</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C22" s="11" t="str">
         <f>VLOOKUP(A22,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="13">
         <f>VLOOKUP(A22,[2]TDSheet!$A:$T,14,0)</f>
         <v>235.131</v>
       </c>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="11">
         <v>25</v>
       </c>
-      <c r="C23" t="str">
+      <c r="C23" s="11" t="str">
         <f>VLOOKUP(A23,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="13">
         <f>VLOOKUP(A23,[2]TDSheet!$A:$T,14,0)</f>
         <v>0</v>
       </c>
-      <c r="E23" t="s">
-        <v>126</v>
+      <c r="E23" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>0.3</v>
       </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="11">
         <v>6</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C25" s="11" t="str">
         <f>VLOOKUP(A25,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="13">
         <f>VLOOKUP(A25,[2]TDSheet!$A:$T,14,0)</f>
         <v>41.41</v>
       </c>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="11">
         <v>35</v>
       </c>
-      <c r="C26" t="str">
+      <c r="C26" s="11" t="str">
         <f>VLOOKUP(A26,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="13">
         <v>0</v>
       </c>
-      <c r="E26" t="b">
-        <f t="shared" ref="E25:E28" si="0">D26&lt;B26</f>
-        <v>1</v>
+      <c r="E26" s="11" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="11">
         <v>12.71</v>
       </c>
-      <c r="C27" t="str">
+      <c r="C27" s="11" t="str">
         <f>VLOOKUP(A27,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="13">
         <f>VLOOKUP(A27,[2]TDSheet!$A:$T,14,0)</f>
         <v>2.0499999999999998</v>
       </c>
-      <c r="E27" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E27" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="11">
         <v>4</v>
       </c>
-      <c r="C28" t="str">
+      <c r="C28" s="11" t="str">
         <f>VLOOKUP(A28,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="13">
         <f>VLOOKUP(A28,[2]TDSheet!$A:$T,14,0)</f>
         <v>85.921000000000006</v>
       </c>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="3">
         <v>1.2</v>
       </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="11">
         <v>4</v>
       </c>
-      <c r="C30" t="str">
+      <c r="C30" s="11" t="str">
         <f>VLOOKUP(A30,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="13">
         <f>VLOOKUP(A30,[2]TDSheet!$A:$T,14,0)</f>
         <v>0</v>
       </c>
-      <c r="E30" t="b">
-        <f t="shared" ref="E30" si="1">D30&lt;B30</f>
-        <v>1</v>
+      <c r="E30" s="11" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="3">
         <v>1.64</v>
       </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="11">
         <v>3.3319999999999999</v>
       </c>
-      <c r="C32" t="str">
+      <c r="C32" s="11" t="str">
         <f>VLOOKUP(A32,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="13">
         <f>VLOOKUP(A32,[2]TDSheet!$A:$T,14,0)</f>
         <v>10.847</v>
       </c>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="3">
         <v>1.4</v>
       </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="3">
         <v>1.23</v>
       </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="3">
         <v>1.5</v>
       </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="3">
         <v>0.72</v>
       </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="11">
         <v>5.95</v>
       </c>
-      <c r="C37" t="str">
+      <c r="C37" s="11" t="str">
         <f>VLOOKUP(A37,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="13">
         <f>VLOOKUP(A37,[2]TDSheet!$A:$T,14,0)</f>
         <v>2.8</v>
       </c>
-      <c r="E37" t="b">
-        <f t="shared" ref="E37:E40" si="2">D37&lt;B37</f>
-        <v>1</v>
+      <c r="E37" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="11">
         <v>15.7</v>
       </c>
-      <c r="C38" t="str">
+      <c r="C38" s="11" t="str">
         <f>VLOOKUP(A38,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="13">
         <f>VLOOKUP(A38,[2]TDSheet!$A:$T,14,0)</f>
         <v>0</v>
       </c>
-      <c r="E38" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+      <c r="E38" s="11" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="11">
         <v>20.399999999999999</v>
       </c>
-      <c r="C39" t="str">
+      <c r="C39" s="11" t="str">
         <f>VLOOKUP(A39,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="13">
         <f>VLOOKUP(A39,[2]TDSheet!$A:$T,14,0)</f>
         <v>1.4</v>
       </c>
-      <c r="E39" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+      <c r="E39" s="11" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="11">
         <v>26.6</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C40" s="11" t="str">
         <f>VLOOKUP(A40,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="13">
         <f>VLOOKUP(A40,[2]TDSheet!$A:$T,14,0)</f>
         <v>0</v>
       </c>
-      <c r="E40" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+      <c r="E40" s="11" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="3">
         <v>1.4</v>
       </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="11">
         <v>5.04</v>
       </c>
-      <c r="C42" t="str">
+      <c r="C42" s="11" t="str">
         <f>VLOOKUP(A42,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="13">
         <f>VLOOKUP(A42,[2]TDSheet!$A:$T,14,0)</f>
         <v>1.1200000000000001</v>
       </c>
-      <c r="E42" t="b">
-        <f t="shared" ref="E42:E44" si="3">D42&lt;B42</f>
-        <v>1</v>
+      <c r="E42" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="11">
         <v>18.760000000000002</v>
       </c>
-      <c r="C43" t="str">
+      <c r="C43" s="11" t="str">
         <f>VLOOKUP(A43,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="13">
         <f>VLOOKUP(A43,[2]TDSheet!$A:$T,14,0)</f>
         <v>0</v>
       </c>
-      <c r="E43" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
+      <c r="E43" s="11" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="11">
         <v>5.04</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C44" s="11" t="str">
         <f>VLOOKUP(A44,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="13">
         <f>VLOOKUP(A44,[2]TDSheet!$A:$T,14,0)</f>
         <v>10.92</v>
       </c>
+      <c r="E44" s="11"/>
     </row>
     <row r="45" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="3">
         <v>0.4</v>
       </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="3">
         <v>0.12</v>
       </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="3">
         <v>1.35</v>
       </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
     </row>
     <row r="48" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="3">
         <v>0.15</v>
       </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="11">
         <v>2.85</v>
       </c>
-      <c r="C49" t="str">
+      <c r="C49" s="11" t="str">
         <f>VLOOKUP(A49,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="13">
         <f>VLOOKUP(A49,[2]TDSheet!$A:$T,14,0)</f>
         <v>0</v>
       </c>
-      <c r="E49" t="b">
-        <f t="shared" ref="E49" si="4">D49&lt;B49</f>
-        <v>1</v>
+      <c r="E49" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="3">
         <v>1.1200000000000001</v>
       </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="3">
         <v>1.64</v>
       </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="6">
+      <c r="B52" s="3">
         <v>2</v>
       </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="3">
         <v>0.78</v>
       </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="3">
         <v>0.4</v>
       </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
     </row>
     <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="11">
         <v>5.6</v>
       </c>
-      <c r="C55" t="str">
+      <c r="C55" s="11" t="str">
         <f>VLOOKUP(A55,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="13">
         <f>VLOOKUP(A55,[2]TDSheet!$A:$T,14,0)</f>
         <v>17.149999999999999</v>
       </c>
+      <c r="E55" s="11"/>
     </row>
     <row r="56" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="3">
         <v>0.7</v>
       </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
     </row>
     <row r="57" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57" s="3">
         <v>0.66</v>
       </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
     </row>
     <row r="58" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="3">
         <v>0.4</v>
       </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
     </row>
     <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="11">
         <v>14.8</v>
       </c>
-      <c r="C59" t="str">
+      <c r="C59" s="11" t="str">
         <f>VLOOKUP(A59,[1]Sheet!$A:$I,9,0)</f>
         <v>матрица</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="13">
         <f>VLOOKUP(A59,[2]TDSheet!$A:$T,14,0)</f>
         <v>108</v>
       </c>
+      <c r="E59" s="11"/>
     </row>
     <row r="60" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
@@ -14120,6 +14236,7 @@
       <c r="B60" s="7">
         <v>0.9</v>
       </c>
+      <c r="D60"/>
     </row>
     <row r="61" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
@@ -14128,6 +14245,7 @@
       <c r="B61" s="5">
         <v>0.54</v>
       </c>
+      <c r="D61"/>
     </row>
     <row r="62" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
@@ -14136,6 +14254,7 @@
       <c r="B62" s="6">
         <v>1</v>
       </c>
+      <c r="D62"/>
     </row>
     <row r="63" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
@@ -14144,6 +14263,7 @@
       <c r="B63" s="6">
         <v>1</v>
       </c>
+      <c r="D63"/>
     </row>
     <row r="64" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
@@ -14152,6 +14272,7 @@
       <c r="B64" s="7">
         <v>0.2</v>
       </c>
+      <c r="D64"/>
     </row>
     <row r="65" spans="2:2" ht="15" x14ac:dyDescent="0.2">
       <c r="B65" s="8">
@@ -14175,22 +14296,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C58D8AB-F828-4C4C-8F11-6984C09B8438}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="81.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="72.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>116</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>117</v>
       </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>97</v>
       </c>
@@ -14198,7 +14327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>98</v>
       </c>
@@ -14206,7 +14335,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>99</v>
       </c>
@@ -14214,95 +14343,172 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="12">
         <v>20.88</v>
       </c>
+      <c r="C5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="12">
+        <f>VLOOKUP(A5,[2]TDSheet!$A:$T,14,0)</f>
+        <v>4.08</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>137</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B6" s="5">
         <v>0.48</v>
       </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="12">
         <v>2.4</v>
       </c>
+      <c r="C7" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="12">
+        <f>VLOOKUP(A7,[2]TDSheet!$A:$T,14,0)</f>
+        <v>94.56</v>
+      </c>
+      <c r="E7" s="16"/>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="12">
         <v>1.92</v>
       </c>
+      <c r="C8" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="12">
+        <f>VLOOKUP(A8,[2]TDSheet!$A:$T,14,0)</f>
+        <v>168.96</v>
+      </c>
+      <c r="E8" s="16"/>
     </row>
-    <row r="9" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B9" s="5">
         <v>0.18</v>
       </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="12">
         <v>1.2</v>
       </c>
+      <c r="C10" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="12">
         <v>3</v>
       </c>
+      <c r="C11" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="12">
+        <f>VLOOKUP(A11,[2]TDSheet!$A:$T,14,0)</f>
+        <v>60.75</v>
+      </c>
+      <c r="E11" s="16"/>
     </row>
-    <row r="12" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B12" s="7">
         <v>0.7</v>
       </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
     </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="12">
         <v>3.36</v>
       </c>
+      <c r="C13" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="12">
+        <f>VLOOKUP(A13,[2]TDSheet!$A:$T,14,0)</f>
+        <v>57.4</v>
+      </c>
+      <c r="E13" s="16"/>
     </row>
-    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="12">
         <v>2.1</v>
       </c>
+      <c r="C14" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="12">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>140</v>
+      </c>
     </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="12">
         <v>2.4</v>
       </c>
+      <c r="C15" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" s="12">
+        <f>VLOOKUP(A15,[2]TDSheet!$A:$T,14,0)</f>
+        <v>25.8</v>
+      </c>
+      <c r="E15" s="16"/>
     </row>
-    <row r="16" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>114</v>
       </c>
@@ -14340,22 +14546,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC224C02-BE6C-485F-B015-F44742E806E2}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="81.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="96.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>116</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>117</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -14363,7 +14573,7 @@
         <v>1.867</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14371,287 +14581,367 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="12">
         <v>4.17</v>
       </c>
+      <c r="C4" s="12">
+        <f>VLOOKUP(A4,[2]TDSheet!$A:$T,14,0)</f>
+        <v>693.57899999999995</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="12">
         <v>10</v>
       </c>
+      <c r="C5" s="12">
+        <f>VLOOKUP(A5,[2]TDSheet!$A:$T,14,0)</f>
+        <v>926.96799999999996</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="12">
         <v>9.6</v>
       </c>
+      <c r="C6" s="12">
+        <f>VLOOKUP(A6,[2]TDSheet!$A:$T,14,0)</f>
+        <v>84.974000000000004</v>
+      </c>
     </row>
-    <row r="7" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="7">
         <v>0.8</v>
       </c>
+      <c r="C7" s="12"/>
     </row>
-    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="12">
         <v>10.4</v>
       </c>
+      <c r="C8" s="12">
+        <f>VLOOKUP(A8,[2]TDSheet!$A:$T,14,0)</f>
+        <v>465.42399999999998</v>
+      </c>
     </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="12">
         <v>5.14</v>
       </c>
+      <c r="C9" s="12">
+        <f>VLOOKUP(A9,[2]TDSheet!$A:$T,14,0)</f>
+        <v>91.888000000000005</v>
+      </c>
     </row>
-    <row r="10" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="7">
         <v>1.6</v>
       </c>
+      <c r="C10" s="12"/>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="12">
         <v>6.6</v>
       </c>
+      <c r="C11" s="12">
+        <f>VLOOKUP(A11,[2]TDSheet!$A:$T,14,0)</f>
+        <v>554.94399999999996</v>
+      </c>
     </row>
-    <row r="12" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="7">
         <v>1.3</v>
       </c>
+      <c r="C12" s="12"/>
     </row>
-    <row r="13" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="7">
         <v>1.3</v>
       </c>
+      <c r="C13" s="12"/>
     </row>
-    <row r="14" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="5">
         <v>1.35</v>
       </c>
+      <c r="C14" s="12"/>
     </row>
-    <row r="15" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="5">
         <v>0.85</v>
       </c>
+      <c r="C15" s="12"/>
     </row>
-    <row r="16" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="4">
         <v>1.8520000000000001</v>
       </c>
+      <c r="C16" s="12"/>
     </row>
-    <row r="17" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="7">
         <v>0.7</v>
       </c>
+      <c r="C17" s="12"/>
     </row>
-    <row r="18" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="7">
         <v>0.8</v>
       </c>
+      <c r="C18" s="12"/>
     </row>
-    <row r="19" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="7">
         <v>1.3</v>
       </c>
+      <c r="C19" s="12"/>
     </row>
-    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="12">
         <v>2.6</v>
       </c>
+      <c r="C20" s="12">
+        <f>VLOOKUP(A20,[2]TDSheet!$A:$T,14,0)</f>
+        <v>217.51400000000001</v>
+      </c>
     </row>
-    <row r="21" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="7">
         <v>1.6</v>
       </c>
+      <c r="C21" s="12"/>
     </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="12">
         <v>2.6</v>
       </c>
+      <c r="C22" s="12">
+        <f>VLOOKUP(A22,[2]TDSheet!$A:$T,14,0)</f>
+        <v>153.96199999999999</v>
+      </c>
     </row>
-    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="12">
         <v>2.71</v>
       </c>
+      <c r="C23" s="12">
+        <f>VLOOKUP(A23,[2]TDSheet!$A:$T,14,0)</f>
+        <v>150.017</v>
+      </c>
     </row>
-    <row r="24" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="4">
         <v>0.68100000000000005</v>
       </c>
+      <c r="C24" s="12"/>
     </row>
-    <row r="25" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="4">
         <v>0.16800000000000001</v>
       </c>
+      <c r="C25" s="12"/>
     </row>
-    <row r="26" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="4">
         <v>0.17199999999999999</v>
       </c>
+      <c r="C26" s="12"/>
     </row>
-    <row r="27" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B27" s="7">
         <v>1.8</v>
       </c>
+      <c r="C27" s="12"/>
     </row>
-    <row r="28" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B28" s="7">
         <v>1.8</v>
       </c>
+      <c r="C28" s="12"/>
     </row>
-    <row r="29" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B29" s="7">
         <v>1.8</v>
       </c>
+      <c r="C29" s="12"/>
     </row>
-    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="12">
         <v>5.7</v>
       </c>
+      <c r="C30" s="12">
+        <f>VLOOKUP(A30,[2]TDSheet!$A:$T,14,0)</f>
+        <v>219.19900000000001</v>
+      </c>
     </row>
-    <row r="31" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="4">
         <v>0.499</v>
       </c>
+      <c r="C31" s="12"/>
     </row>
-    <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="12">
         <v>4.2190000000000003</v>
       </c>
+      <c r="C32" s="12">
+        <f>VLOOKUP(A32,[2]TDSheet!$A:$T,14,0)</f>
+        <v>616.33399999999995</v>
+      </c>
     </row>
-    <row r="33" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="12">
         <v>3.7509999999999999</v>
       </c>
+      <c r="C33" s="12">
+        <f>VLOOKUP(A33,[2]TDSheet!$A:$T,14,0)</f>
+        <v>491.60599999999999</v>
+      </c>
     </row>
-    <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A34" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="12">
         <v>7.2309999999999999</v>
       </c>
+      <c r="C34" s="12">
+        <f>VLOOKUP(A34,[2]TDSheet!$A:$T,14,0)</f>
+        <v>145.46600000000001</v>
+      </c>
     </row>
-    <row r="35" spans="1:2" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B35" s="4">
         <v>0.32800000000000001</v>
       </c>
+      <c r="C35" s="12"/>
     </row>
-    <row r="36" spans="1:2" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B36" s="7">
         <v>0.7</v>
       </c>
+      <c r="C36" s="12"/>
     </row>
-    <row r="37" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
+    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A37" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="12">
         <v>3.36</v>
       </c>
+      <c r="C37" s="12">
+        <f>VLOOKUP(A37,[2]TDSheet!$A:$T,14,0)</f>
+        <v>33.32</v>
+      </c>
     </row>
-    <row r="38" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="12">
         <v>3.01</v>
       </c>
+      <c r="C38" s="12">
+        <f>VLOOKUP(A38,[2]TDSheet!$A:$T,14,0)</f>
+        <v>645.65200000000004</v>
+      </c>
     </row>
-    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="B39" s="8">
         <f>SUM(B2:B38)</f>
         <v>104.90799999999997</v>
